--- a/Assets/Excel/RoleAttr.xlsx
+++ b/Assets/Excel/RoleAttr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A0F683-7DF4-45E2-BA76-AADCEAF0520A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218683AB-E79D-47E5-B67F-F4C1B1593431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="1950" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30105" yWindow="1545" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>ID索引</t>
   </si>
@@ -140,6 +140,34 @@
   </si>
   <si>
     <t>LifeStealRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -480,15 +508,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -498,8 +528,14 @@
       <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -509,8 +545,14 @@
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -520,8 +562,14 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -531,8 +579,14 @@
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="1">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -542,8 +596,14 @@
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -553,8 +613,14 @@
       <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="1">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -564,8 +630,14 @@
       <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -575,8 +647,14 @@
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -586,8 +664,14 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -597,8 +681,14 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -608,8 +698,14 @@
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -619,8 +715,14 @@
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -630,8 +732,14 @@
       <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -640,6 +748,12 @@
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/RoleAttr.xlsx
+++ b/Assets/Excel/RoleAttr.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218683AB-E79D-47E5-B67F-F4C1B1593431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B85FF9-F0F9-4785-86CE-240AC984FA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30105" yWindow="1545" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30045" yWindow="1530" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>ID索引</t>
   </si>
@@ -91,14 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>敏捷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +169,66 @@
   </si>
   <si>
     <t>百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化爆伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终增伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终减伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化治疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱化宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageIncrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageDecrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AntiHealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetIncrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PetDecrease</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -200,12 +261,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -220,12 +299,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -508,11 +596,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
@@ -529,10 +617,10 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -546,7 +634,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>3</v>
@@ -563,17 +651,17 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -583,14 +671,14 @@
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -600,14 +688,14 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -617,143 +705,377 @@
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
+      <c r="B10" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
+      <c r="B12" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
+      <c r="B14" s="5" t="str">
+        <f>"Anti"&amp;B8</f>
+        <v>AntiCritRate</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f>"抗"&amp;C8</f>
+        <v>抗暴击</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" ref="B15:B19" si="0">"Anti"&amp;B9</f>
+        <v>AntiCounterRate</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f t="shared" ref="C15:C19" si="1">"抗"&amp;C9</f>
+        <v>抗反击</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>AntiComboRate</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>抗连击</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>AntiDodgeRate</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>抗闪避</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>AntiStunRate</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>抗击晕</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>AntiLifeStealRate</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>抗吸血</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="D20" s="1">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>"Anti"&amp;B20</f>
+        <v>AntiCritDmg</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/RoleAttr.xlsx
+++ b/Assets/Excel/RoleAttr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B85FF9-F0F9-4785-86CE-240AC984FA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536830BB-884F-4724-BE97-694D1285FBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30045" yWindow="1530" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Excel/RoleAttr.xlsx
+++ b/Assets/Excel/RoleAttr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536830BB-884F-4724-BE97-694D1285FBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57D4022-6443-448D-B0ED-37CB2874D2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>ID索引</t>
   </si>
@@ -229,6 +229,14 @@
   </si>
   <si>
     <t>PetDecrease</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CombatPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,17 +604,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,8 +630,11 @@
       <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -639,8 +650,11 @@
       <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -656,8 +670,11 @@
       <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -673,8 +690,11 @@
       <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -690,8 +710,11 @@
       <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -707,8 +730,11 @@
       <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -724,8 +750,11 @@
       <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -741,8 +770,11 @@
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -758,8 +790,11 @@
       <c r="E9" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -775,8 +810,11 @@
       <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -792,8 +830,11 @@
       <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -809,8 +850,11 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -826,8 +870,11 @@
       <c r="E13" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -845,8 +892,11 @@
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -864,8 +914,11 @@
       <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -883,8 +936,11 @@
       <c r="E16" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -902,8 +958,11 @@
       <c r="E17" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -921,8 +980,11 @@
       <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -940,8 +1002,11 @@
       <c r="E19" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -957,8 +1022,11 @@
       <c r="E20" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -975,8 +1043,11 @@
       <c r="E21" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -992,8 +1063,11 @@
       <c r="E22" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1009,8 +1083,11 @@
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1026,8 +1103,11 @@
       <c r="E24" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1043,8 +1123,11 @@
       <c r="E25" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1060,8 +1143,11 @@
       <c r="E26" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1076,6 +1162,9 @@
       </c>
       <c r="E27" s="1" t="s">
         <v>34</v>
+      </c>
+      <c r="F27" s="1">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
